--- a/data/trans_orig/IQ09_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,1</t>
+          <t>0,73; 3,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,9</t>
+          <t>0,47; 4,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,29</t>
+          <t>0,58; 2,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,82</t>
+          <t>0,05; 2,85</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,4</t>
+          <t>0,26; 2,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,52</t>
+          <t>0,72; 2,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,22</t>
+          <t>0,7; 3,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,98</t>
+          <t>0,49; 1,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,43</t>
+          <t>0,76; 3,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,17</t>
+          <t>1,02; 3,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,7</t>
+          <t>0,7; 2,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,92</t>
+          <t>0,44; 1,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,51</t>
+          <t>0,69; 2,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,45</t>
+          <t>1,14; 2,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,35</t>
+          <t>0,89; 2,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,63</t>
+          <t>0,56; 1,58</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 6,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,4</t>
+          <t>0,14; 1,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,18</t>
+          <t>0,43; 2,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,39</t>
+          <t>0,93; 5,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,24</t>
+          <t>0,47; 6,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,04</t>
+          <t>0,53; 2,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,15</t>
+          <t>1,15; 4,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,14</t>
+          <t>0,48; 4,49</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,0</t>
+          <t>0,28; 2,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,0</t>
+          <t>0,7; 2,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,79</t>
+          <t>0,75; 2,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,36</t>
+          <t>0,28; 1,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,37</t>
+          <t>0,51; 2,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,66</t>
+          <t>1,17; 2,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,95</t>
+          <t>0,96; 2,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,42</t>
+          <t>0,72; 2,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,89</t>
+          <t>0,58; 1,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,09</t>
+          <t>1,08; 2,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,39</t>
+          <t>1,08; 2,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,67</t>
+          <t>0,65; 1,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Estudios-trans_orig.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,15</t>
+          <t>0,82; 3,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,14</t>
+          <t>0,44; 4,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,31</t>
+          <t>0,58; 2,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,85</t>
+          <t>0,09; 2,77</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,3</t>
+          <t>0,25; 2,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,46</t>
+          <t>0,68; 2,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,42</t>
+          <t>0,61; 3,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,95</t>
+          <t>0,48; 2,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,17</t>
+          <t>0,71; 3,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,31</t>
+          <t>1,0; 3,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,73</t>
+          <t>0,73; 2,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,91</t>
+          <t>0,41; 1,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,55</t>
+          <t>0,72; 2,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,46</t>
+          <t>1,1; 2,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,54</t>
+          <t>0,88; 2,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,58</t>
+          <t>0,53; 1,57</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,0</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,3</t>
+          <t>0,2; 1,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,3</t>
+          <t>0,99; 5,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,59</t>
+          <t>0,49; 6,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,04</t>
+          <t>0,56; 2,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,17</t>
+          <t>1,16; 4,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,49</t>
+          <t>0,5; 3,81</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,16</t>
+          <t>0,23; 1,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,05</t>
+          <t>0,76; 2,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,86</t>
+          <t>0,74; 2,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,37</t>
+          <t>0,28; 1,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,28</t>
+          <t>0,5; 2,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,63</t>
+          <t>1,15; 2,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>1,06; 2,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,34</t>
+          <t>0,81; 2,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,97</t>
+          <t>0,59; 1,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,07</t>
+          <t>1,1; 2,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,43</t>
+          <t>1,09; 2,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,7</t>
+          <t>0,67; 1,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -653,44 +653,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,03</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,69</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>1,25</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,84</t>
         </is>
       </c>
     </row>
@@ -721,47 +721,47 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,75; 3,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,48; 4,11</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,7</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0,0; 3,0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,82; 3,2</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 4,08</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,37</t>
+          <t>0,56; 2,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,77</t>
+          <t>0,67; 3,63</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,71</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,87</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,43</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,53</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,01</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,92</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,25</t>
+          <t>0,74; 3,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,47</t>
+          <t>0,98; 3,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,14</t>
+          <t>0,69; 2,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,04</t>
+          <t>0,38; 1,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,34</t>
+          <t>0,19; 2,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,2</t>
+          <t>0,77; 2,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,74</t>
+          <t>0,57; 3,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,98</t>
+          <t>0,46; 1,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,66</t>
+          <t>0,69; 2,51</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,49</t>
+          <t>1,12; 2,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,4</t>
+          <t>0,84; 2,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,57</t>
+          <t>0,52; 1,57</t>
         </is>
       </c>
     </row>
@@ -928,54 +928,54 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,26</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,85</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2,55</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,52</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,42; 2,18</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1,01; 5,39</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,5; 6,24</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 4,52</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,49</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,67</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 1,36</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,79</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,17</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,39</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,07</t>
+          <t>0,18; 1,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,17</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,08</t>
+          <t>0,55; 2,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,19</t>
+          <t>1,16; 4,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,81</t>
+          <t>0,6; 4,25</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,52</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,94</t>
+          <t>0,51; 2,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,04</t>
+          <t>1,15; 2,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,8</t>
+          <t>1,11; 2,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,31</t>
+          <t>0,76; 2,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,28</t>
+          <t>0,28; 2,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,72</t>
+          <t>0,74; 2,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,87</t>
+          <t>0,73; 2,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,41</t>
+          <t>0,54; 1,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,25</t>
+          <t>1,1; 2,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,39</t>
+          <t>1,1; 2,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,69</t>
+          <t>0,8; 1,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
+          <t>Tiempo medio en meses que los menores llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,255 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.676107115401224</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.026643361504531</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.6903012540538822</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>0.4028947903861402</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1.259900460060363</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>1.246965811789929</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0.1959631905405024</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>1.842058009430318</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 3,1</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,48; 4,11</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,7</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 2,29</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,71</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,67; 3,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0.7452501098526316</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>0.4760906190382734</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="n">
+        <v>0.559448953173136</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.6696866782555004</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>3.095128903937299</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>4.110952706527083</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>2.699091369511318</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="n">
+        <v>2.287392818857666</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.7111695423954684</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>3.632712673557167</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 3,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,98; 3,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,69; 2,7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 1,77</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,19; 2,4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,77; 2,52</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,57; 3,22</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 1,97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,69; 2,51</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 2,45</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>0,84; 2,35</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 1,57</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.714388711507582</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.853074475517866</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.499693318827324</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.8621145910780406</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.869963292633758</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.429778670727748</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1.528670821199199</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.00353953220384</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.399974636013823</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.661266511935872</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1.513132648584852</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0.9210383535942808</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2,55</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7396132500107421</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9797296123043218</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6880730300035716</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.3834730570799796</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.1931553835457746</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.7666900712681544</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.572737244341029</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.4609465217084397</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.6916500221202314</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.124827455401575</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0.842247144433163</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.5246167424833601</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,75</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,42; 2,18</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,01; 5,39</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,5; 6,24</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,52</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,47</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,6</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 1,74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,42</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0,55; 2,04</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 4,15</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 4,25</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.429525905572154</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.168687123183473</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.700770087633335</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.772497528062835</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>2.402182249747689</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2.523243695131636</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>3.22200228464904</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1.974363065071085</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>2.511487453254402</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>2.451725370576825</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2.349333660558098</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1.567595719721506</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +907,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.4233564514759923</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.255760614676086</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>3.099253711883123</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.285588270510104</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>1.320273771346441</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.261183575182113</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.850091786613094</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0.7396596395123156</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0.770491853556982</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1.258091715850732</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>2.545702372042475</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.521666425013657</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 2,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 2,66</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 2,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 2,43</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 2,0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 2,0</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 2,79</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 1,61</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 1,89</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 2,09</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 2,39</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,8; 1,79</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4173939470469373</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.009135666665912</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.500038970021055</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.1785743039268541</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0.55054407644263</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.160512107976657</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0.5976845968113275</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.749572449353839</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.179050185806461</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.389066060887906</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.237053627678761</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>4.517844663902948</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.4738842952602</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>4.59761670748681</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>1.742466096836164</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>2.423540423420035</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>2.037959596869466</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>4.145696750100129</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>4.252644531671788</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.167296433376911</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.740065232741119</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.797711188963817</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.353373606541376</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.8409027343496931</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1.266231700892254</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.52049336977896</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.9538646105745465</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1.045449007429395</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1.528415837243488</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1.670083644795906</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1.190212298740964</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5129839542099085</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.153774129576893</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.107789005976223</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.7629031590558345</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.2775037270853154</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.7441950134945083</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0.7288295946140068</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0.5423756588500399</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0.587063887217144</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.097662253162223</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.09607276225612</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0.7969359973545388</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.367807184986848</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.664175506895318</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.947229504222053</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.430300423455491</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>2.003335847039142</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2.000566663112875</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.787070895355545</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>1.607979472326294</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1.890215384103898</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>2.086061910788167</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>2.389178314634862</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1.794806100107733</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1177,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
